--- a/output/laminas_comunales/comunal_s_fonasa_a_2021_metropolitana.xlsx
+++ b/output/laminas_comunales/comunal_s_fonasa_a_2021_metropolitana.xlsx
@@ -375,136 +375,136 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>13201</t>
+          <t>13112</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Puente Alto</t>
+          <t>La Pintana</t>
         </is>
       </c>
       <c r="C2">
-        <v>434857</v>
+        <v>91.02114660594719</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>13101</t>
+          <t>13505</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Santiago</t>
+          <t>San Pedro</t>
         </is>
       </c>
       <c r="C3">
-        <v>418968</v>
+        <v>88.56027931813514</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>13119</t>
+          <t>13103</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Maipú</t>
+          <t>Cerro Navia</t>
         </is>
       </c>
       <c r="C4">
-        <v>355715</v>
+        <v>88.26523276878396</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>13110</t>
+          <t>13116</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>La Florida</t>
+          <t>Lo Espejo</t>
         </is>
       </c>
       <c r="C5">
-        <v>255801</v>
+        <v>87.89504059863079</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>13401</t>
+          <t>13504</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>San Bernardo</t>
+          <t>María Pinto</t>
         </is>
       </c>
       <c r="C6">
-        <v>241499</v>
+        <v>86.75745016775213</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>13122</t>
+          <t>13131</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Peñalolén</t>
+          <t>San Ramón</t>
         </is>
       </c>
       <c r="C7">
-        <v>172264</v>
+        <v>86.60432562675693</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>13124</t>
+          <t>13501</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Pudahuel</t>
+          <t>Melipilla</t>
         </is>
       </c>
       <c r="C8">
-        <v>170421</v>
+        <v>86.20342612419701</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>13112</t>
+          <t>13602</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>La Pintana</t>
+          <t>El Monte</t>
         </is>
       </c>
       <c r="C9">
-        <v>161497</v>
+        <v>86.03855966753466</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>13125</t>
+          <t>13111</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Quilicura</t>
+          <t>La Granja</t>
         </is>
       </c>
       <c r="C10">
-        <v>154930</v>
+        <v>85.52336300461337</v>
       </c>
     </row>
     <row r="11">
@@ -519,622 +519,622 @@
         </is>
       </c>
       <c r="C11">
-        <v>138633</v>
+        <v>85.42721928494842</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>13127</t>
+          <t>13117</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Lo Prado</t>
         </is>
       </c>
       <c r="C12">
-        <v>137670</v>
+        <v>84.55804593570645</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>13106</t>
+          <t>13128</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Estación Central</t>
+          <t>Renca</t>
         </is>
       </c>
       <c r="C13">
-        <v>133728</v>
+        <v>84.31851556102941</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>13128</t>
+          <t>13404</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Renca</t>
+          <t>Paine</t>
         </is>
       </c>
       <c r="C14">
-        <v>124600</v>
+        <v>84.05644595542604</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>13103</t>
+          <t>13121</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Cerro Navia</t>
+          <t>Pedro Aguirre Cerda</t>
         </is>
       </c>
       <c r="C15">
-        <v>122784</v>
+        <v>83.4837484534896</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>13501</t>
+          <t>13603</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Melipilla</t>
+          <t>Isla de Maipo</t>
         </is>
       </c>
       <c r="C16">
-        <v>120771</v>
+        <v>82.69749203496447</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>13104</t>
+          <t>13503</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Conchalí</t>
+          <t>Curacaví</t>
         </is>
       </c>
       <c r="C17">
-        <v>107386</v>
+        <v>82.07906883403572</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>13126</t>
+          <t>13104</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Quinta Normal</t>
+          <t>Conchalí</t>
         </is>
       </c>
       <c r="C18">
-        <v>102824</v>
+        <v>82.00346689270197</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>13111</t>
+          <t>13401</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>La Granja</t>
+          <t>San Bernardo</t>
         </is>
       </c>
       <c r="C19">
-        <v>102516</v>
+        <v>80.82701608179795</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>13301</t>
+          <t>13127</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Colina</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="C20">
-        <v>92306</v>
+        <v>80.79841771966171</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>13108</t>
+          <t>13129</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Independencia</t>
+          <t>San Joaquín</t>
         </is>
       </c>
       <c r="C21">
-        <v>91179</v>
+        <v>79.74718356202057</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>13120</t>
+          <t>13502</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Ñuñoa</t>
+          <t>Alhué</t>
         </is>
       </c>
       <c r="C22">
-        <v>89740</v>
+        <v>79.54173486088379</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>13116</t>
+          <t>13126</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Lo Espejo</t>
+          <t>Quinta Normal</t>
         </is>
       </c>
       <c r="C23">
-        <v>88331</v>
+        <v>79.00422589320016</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>13121</t>
+          <t>13605</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Pedro Aguirre Cerda</t>
+          <t>Peñaflor</t>
         </is>
       </c>
       <c r="C24">
-        <v>87046</v>
+        <v>78.5010242714802</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>13118</t>
+          <t>13601</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Macul</t>
+          <t>Talagante</t>
         </is>
       </c>
       <c r="C25">
-        <v>83315</v>
+        <v>78.1931049182075</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>13402</t>
+          <t>13201</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Buin</t>
+          <t>Puente Alto</t>
         </is>
       </c>
       <c r="C26">
-        <v>82993</v>
+        <v>77.51599850264711</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>13117</t>
+          <t>13108</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Lo Prado</t>
+          <t>Independencia</t>
         </is>
       </c>
       <c r="C27">
-        <v>82357</v>
+        <v>77.4883570724411</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>13129</t>
+          <t>13102</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>San Joaquín</t>
+          <t>Cerrillos</t>
         </is>
       </c>
       <c r="C28">
-        <v>81193</v>
+        <v>77.31402334782396</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>13302</t>
+          <t>13203</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Lampa</t>
+          <t>San José de Maipo</t>
         </is>
       </c>
       <c r="C29">
-        <v>80326</v>
+        <v>77.13500168331277</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>13130</t>
+          <t>13124</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Pudahuel</t>
         </is>
       </c>
       <c r="C30">
-        <v>80094</v>
+        <v>76.96104552967422</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>13131</t>
+          <t>13106</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>San Ramón</t>
+          <t>Estación Central</t>
         </is>
       </c>
       <c r="C31">
-        <v>75480</v>
+        <v>76.9183869501947</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>13114</t>
+          <t>13604</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Las Condes</t>
+          <t>Padre Hurtado</t>
         </is>
       </c>
       <c r="C32">
-        <v>73351</v>
+        <v>76.61145589303084</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>13605</t>
+          <t>13402</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Peñaflor</t>
+          <t>Buin</t>
         </is>
       </c>
       <c r="C33">
-        <v>73192</v>
+        <v>76.22778415614236</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>13109</t>
+          <t>13125</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>La Cisterna</t>
+          <t>Quilicura</t>
         </is>
       </c>
       <c r="C34">
-        <v>71807</v>
+        <v>74.64059970708395</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>13102</t>
+          <t>13403</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Cerrillos</t>
+          <t>Calera de Tango</t>
         </is>
       </c>
       <c r="C35">
-        <v>63314</v>
+        <v>73.85466287285399</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>13404</t>
+          <t>13202</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Paine</t>
+          <t>Pirque</t>
         </is>
       </c>
       <c r="C36">
-        <v>62306</v>
+        <v>73.61252755206105</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>13107</t>
+          <t>13109</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Huechuraba</t>
+          <t>La Cisterna</t>
         </is>
       </c>
       <c r="C37">
-        <v>61317</v>
+        <v>73.42679509990388</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>13601</t>
+          <t>13302</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Talagante</t>
+          <t>Lampa</t>
         </is>
       </c>
       <c r="C38">
-        <v>58698</v>
+        <v>72.0599976675548</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>13604</t>
+          <t>13122</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Padre Hurtado</t>
+          <t>Peñalolén</t>
         </is>
       </c>
       <c r="C39">
-        <v>55921</v>
+        <v>71.96256997242878</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>13123</t>
+          <t>13119</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Providencia</t>
+          <t>Maipú</t>
         </is>
       </c>
       <c r="C40">
-        <v>43134</v>
+        <v>70.42160111814572</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>13113</t>
+          <t>13110</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>La Reina</t>
+          <t>La Florida</t>
         </is>
       </c>
       <c r="C41">
-        <v>36564</v>
+        <v>69.07305297380202</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>13115</t>
+          <t>13101</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Lo Barnechea</t>
+          <t>Santiago</t>
         </is>
       </c>
       <c r="C42">
-        <v>33753</v>
+        <v>69.04628102169933</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>13602</t>
+          <t>13118</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>El Monte</t>
+          <t>Macul</t>
         </is>
       </c>
       <c r="C43">
-        <v>32711</v>
+        <v>66.31723061983109</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>13603</t>
+          <t>13107</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Isla de Maipo</t>
+          <t>Huechuraba</t>
         </is>
       </c>
       <c r="C44">
-        <v>30369</v>
+        <v>61.3814505230492</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>13503</t>
+          <t>13301</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Curacaví</t>
+          <t>Colina</t>
         </is>
       </c>
       <c r="C45">
-        <v>28630</v>
+        <v>60.79802929708083</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>13403</t>
+          <t>13130</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Calera de Tango</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="C46">
-        <v>23101</v>
+        <v>57.67801590044936</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>13202</t>
+          <t>13120</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Pirque</t>
+          <t>Ñuñoa</t>
         </is>
       </c>
       <c r="C47">
-        <v>22376</v>
+        <v>40.97978866228891</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>13203</t>
+          <t>13113</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>San José de Maipo</t>
+          <t>La Reina</t>
         </is>
       </c>
       <c r="C48">
-        <v>13747</v>
+        <v>40.55232074530029</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>13504</t>
+          <t>13115</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>María Pinto</t>
+          <t>Lo Barnechea</t>
         </is>
       </c>
       <c r="C49">
-        <v>13188</v>
+        <v>33.74422650110971</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>13132</t>
+          <t>13123</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Vitacura</t>
+          <t>Providencia</t>
         </is>
       </c>
       <c r="C50">
-        <v>11679</v>
+        <v>30.35873902914535</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>13505</t>
+          <t>13114</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>San Pedro</t>
+          <t>Las Condes</t>
         </is>
       </c>
       <c r="C51">
-        <v>8624</v>
+        <v>25.95108455303537</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>13502</t>
+          <t>13132</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Alhué</t>
+          <t>Vitacura</t>
         </is>
       </c>
       <c r="C52">
-        <v>6318</v>
+        <v>14.81880931837791</v>
       </c>
     </row>
   </sheetData>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Personas afiliadas a FONASA</t>
+          <t>Porcentaje de residentes afiliados a FONASA</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
